--- a/scenarios/07_karen_test_engineer/7.3_mtf_measurement_vs_prediction/outputs/mtf_comparison_results.xlsx
+++ b/scenarios/07_karen_test_engineer/7.3_mtf_measurement_vs_prediction/outputs/mtf_comparison_results.xlsx
@@ -596,7 +596,7 @@
         <v>0.9993</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.9999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -610,13 +610,13 @@
         <v>0.8088</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.9772</v>
+        <v>0.9772999999999999</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>-0.1809</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-0.0125</v>
+        <v>-0.0124</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>0.9848</v>
@@ -628,7 +628,7 @@
         <v>0.9985000000000001</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.9999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -642,13 +642,13 @@
         <v>0.8013</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.9663</v>
+        <v>0.9665</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>-0.1329</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.0321</v>
+        <v>0.0323</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>0.9797</v>
@@ -660,7 +660,7 @@
         <v>0.9974</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.9998</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="7">
@@ -674,13 +674,13 @@
         <v>0.795</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.9539</v>
+        <v>0.9540999999999999</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>-0.135</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.0239</v>
+        <v>0.0241</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>0.9747</v>
@@ -692,7 +692,7 @@
         <v>0.996</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.9996</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="8">
@@ -706,13 +706,13 @@
         <v>0.789</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0.9401</v>
+        <v>0.9404</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>-0.1467</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.0044</v>
+        <v>0.0047</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>0.9696</v>
@@ -724,7 +724,7 @@
         <v>0.9944</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.9995000000000001</v>
+        <v>0.9998</v>
       </c>
     </row>
     <row r="9">
@@ -738,13 +738,13 @@
         <v>0.7853</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>0.9248</v>
+        <v>0.9252</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>-0.1262</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.0133</v>
+        <v>0.0137</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>0.9645</v>
@@ -756,7 +756,7 @@
         <v>0.9925</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.9993</v>
+        <v>0.9998</v>
       </c>
     </row>
     <row r="10">
@@ -770,13 +770,13 @@
         <v>0.7814</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>0.9083</v>
+        <v>0.9088000000000001</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>-0.1155</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0.0114</v>
+        <v>0.0119</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>0.9595</v>
@@ -788,7 +788,7 @@
         <v>0.9903999999999999</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.9991</v>
+        <v>0.9997</v>
       </c>
     </row>
     <row r="11">
@@ -802,13 +802,13 @@
         <v>0.776</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>0.8905</v>
+        <v>0.8912</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>-0.0877</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>0.0268</v>
+        <v>0.0275</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>0.9544</v>
@@ -820,7 +820,7 @@
         <v>0.9881</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.9988</v>
+        <v>0.9996</v>
       </c>
     </row>
     <row r="12">
@@ -834,13 +834,13 @@
         <v>0.7704</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>0.8717</v>
+        <v>0.8725000000000001</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>-0.0973</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>0.004</v>
+        <v>0.0048</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>0.9493</v>
@@ -852,7 +852,7 @@
         <v>0.9857</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.9986</v>
+        <v>0.9995000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -866,13 +866,13 @@
         <v>0.7637</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>0.8519</v>
+        <v>0.8528</v>
       </c>
       <c r="E13" s="2" t="n">
         <v>-0.0791</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0.0091</v>
+        <v>0.01</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>0.9443</v>
@@ -884,7 +884,7 @@
         <v>0.9832</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.9983</v>
+        <v>0.9994</v>
       </c>
     </row>
     <row r="14">
@@ -898,13 +898,13 @@
         <v>0.7576000000000001</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>0.8310999999999999</v>
+        <v>0.8323</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>-0.05</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.0235</v>
+        <v>0.0247</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>0.9392</v>
@@ -916,7 +916,7 @@
         <v>0.9806</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0.9979</v>
+        <v>0.9993</v>
       </c>
     </row>
     <row r="15">
@@ -930,13 +930,13 @@
         <v>0.7531</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>0.8095</v>
+        <v>0.8109</v>
       </c>
       <c r="E15" s="2" t="n">
         <v>-0.0448</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>0.0116</v>
+        <v>0.013</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>0.9342</v>
@@ -948,7 +948,7 @@
         <v>0.9781</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.9976</v>
+        <v>0.9992</v>
       </c>
     </row>
     <row r="16">
@@ -962,13 +962,13 @@
         <v>0.7482</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>0.7873</v>
+        <v>0.7887999999999999</v>
       </c>
       <c r="E16" s="2" t="n">
         <v>-0.0133</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>0.0258</v>
+        <v>0.0273</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>0.9291</v>
@@ -980,7 +980,7 @@
         <v>0.9756</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.9972</v>
+        <v>0.9991</v>
       </c>
     </row>
     <row r="17">
@@ -994,13 +994,13 @@
         <v>0.7418</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>0.7644</v>
+        <v>0.766</v>
       </c>
       <c r="E17" s="2" t="n">
         <v>0.0276</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>0.0502</v>
+        <v>0.0518</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>0.924</v>
@@ -1012,7 +1012,7 @@
         <v>0.9731</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.9968</v>
+        <v>0.9989</v>
       </c>
     </row>
     <row r="18">
@@ -1026,13 +1026,13 @@
         <v>0.7356</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>0.741</v>
+        <v>0.7428</v>
       </c>
       <c r="E18" s="2" t="n">
         <v>0.031</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>0.0364</v>
+        <v>0.0382</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>0.919</v>
@@ -1044,7 +1044,7 @@
         <v>0.9707</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.9964</v>
+        <v>0.9988</v>
       </c>
     </row>
     <row r="19">
@@ -1058,13 +1058,13 @@
         <v>0.7298</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>0.7171</v>
+        <v>0.7191</v>
       </c>
       <c r="E19" s="2" t="n">
         <v>0.0738</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>0.0611</v>
+        <v>0.0631</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>0.9139</v>
@@ -1076,7 +1076,7 @@
         <v>0.9686</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.9959</v>
+        <v>0.9986</v>
       </c>
     </row>
     <row r="20">
@@ -1090,13 +1090,13 @@
         <v>0.7238</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>0.6928</v>
+        <v>0.695</v>
       </c>
       <c r="E20" s="2" t="n">
         <v>0.0693</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>0.0383</v>
+        <v>0.0405</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>0.9089</v>
@@ -1108,7 +1108,7 @@
         <v>0.9666</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.9954</v>
+        <v>0.9985000000000001</v>
       </c>
     </row>
     <row r="21">
@@ -1122,13 +1122,13 @@
         <v>0.7176</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>0.6683</v>
+        <v>0.6706</v>
       </c>
       <c r="E21" s="2" t="n">
         <v>0.1064</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>0.0571</v>
+        <v>0.0594</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>0.9038</v>
@@ -1140,7 +1140,7 @@
         <v>0.9648</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.9949</v>
+        <v>0.9983</v>
       </c>
     </row>
     <row r="22">
@@ -1154,13 +1154,13 @@
         <v>0.7124</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>0.6435999999999999</v>
+        <v>0.646</v>
       </c>
       <c r="E22" s="2" t="n">
         <v>0.1328</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>0.064</v>
+        <v>0.0664</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>0.8988</v>
@@ -1172,7 +1172,7 @@
         <v>0.9631999999999999</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.9943</v>
+        <v>0.9981</v>
       </c>
     </row>
     <row r="23">
@@ -1186,13 +1186,13 @@
         <v>0.7089</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>0.6186</v>
+        <v>0.6212</v>
       </c>
       <c r="E23" s="2" t="n">
         <v>0.1664</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>0.0761</v>
+        <v>0.07870000000000001</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>0.8937</v>
@@ -1204,7 +1204,7 @@
         <v>0.962</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.9937</v>
+        <v>0.9979</v>
       </c>
     </row>
     <row r="24">
@@ -1218,13 +1218,13 @@
         <v>0.7043</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>0.5936</v>
+        <v>0.5963000000000001</v>
       </c>
       <c r="E24" s="2" t="n">
         <v>0.1629</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>0.0522</v>
+        <v>0.0549</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>0.8887</v>
@@ -1236,7 +1236,7 @@
         <v>0.961</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.9931</v>
+        <v>0.9977</v>
       </c>
     </row>
     <row r="25">
@@ -1250,13 +1250,13 @@
         <v>0.6983</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>0.5685</v>
+        <v>0.5714</v>
       </c>
       <c r="E25" s="2" t="n">
         <v>0.207</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>0.0772</v>
+        <v>0.0801</v>
       </c>
       <c r="G25" s="2" t="n">
         <v>0.8836000000000001</v>
@@ -1268,7 +1268,7 @@
         <v>0.9604</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.9925</v>
+        <v>0.9975000000000001</v>
       </c>
     </row>
     <row r="26">
@@ -1282,13 +1282,13 @@
         <v>0.6923</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>0.5434</v>
+        <v>0.5464</v>
       </c>
       <c r="E26" s="2" t="n">
         <v>0.2343</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>0.0854</v>
+        <v>0.08840000000000001</v>
       </c>
       <c r="G26" s="2" t="n">
         <v>0.8786</v>
@@ -1300,7 +1300,7 @@
         <v>0.96</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.9918</v>
+        <v>0.9973</v>
       </c>
     </row>
     <row r="27">
@@ -1314,13 +1314,13 @@
         <v>0.6863</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>0.5183</v>
+        <v>0.5214</v>
       </c>
       <c r="E27" s="2" t="n">
         <v>0.256</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.0911</v>
       </c>
       <c r="G27" s="2" t="n">
         <v>0.8735000000000001</v>
@@ -1332,7 +1332,7 @@
         <v>0.96</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.9911</v>
+        <v>0.997</v>
       </c>
     </row>
     <row r="28">
@@ -1343,16 +1343,16 @@
         <v>0.4152</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>0.6803</v>
+        <v>0.6802</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>0.4933</v>
+        <v>0.4964</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>0.2651</v>
+        <v>0.265</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>0.0781</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="G28" s="2" t="n">
         <v>0.8685</v>
@@ -1364,7 +1364,7 @@
         <v>0.9604</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.9903999999999999</v>
+        <v>0.9968</v>
       </c>
     </row>
     <row r="29">
@@ -1378,13 +1378,13 @@
         <v>0.6741</v>
       </c>
       <c r="D29" s="2" t="n">
-        <v>0.4683</v>
+        <v>0.4716</v>
       </c>
       <c r="E29" s="2" t="n">
         <v>0.2892</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>0.0834</v>
+        <v>0.0867</v>
       </c>
       <c r="G29" s="2" t="n">
         <v>0.8635</v>
@@ -1396,7 +1396,7 @@
         <v>0.961</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.9896</v>
+        <v>0.9965000000000001</v>
       </c>
     </row>
     <row r="30">
@@ -1410,13 +1410,13 @@
         <v>0.6684</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>0.4435</v>
+        <v>0.4468</v>
       </c>
       <c r="E30" s="2" t="n">
         <v>0.31</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>0.0851</v>
+        <v>0.08840000000000001</v>
       </c>
       <c r="G30" s="2" t="n">
         <v>0.8584000000000001</v>
@@ -1428,7 +1428,7 @@
         <v>0.962</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.9889</v>
+        <v>0.9963</v>
       </c>
     </row>
     <row r="31">
@@ -1439,16 +1439,16 @@
         <v>0.3322</v>
       </c>
       <c r="C31" s="2" t="n">
-        <v>0.6633</v>
+        <v>0.6632</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>0.4188</v>
+        <v>0.4221</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>0.3311</v>
+        <v>0.331</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>0.0866</v>
+        <v>0.08989999999999999</v>
       </c>
       <c r="G31" s="2" t="n">
         <v>0.8534</v>
@@ -1460,7 +1460,7 @@
         <v>0.9631999999999999</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.9881</v>
+        <v>0.996</v>
       </c>
     </row>
     <row r="32">
@@ -1474,13 +1474,13 @@
         <v>0.6584</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>0.3943</v>
+        <v>0.3976</v>
       </c>
       <c r="E32" s="2" t="n">
         <v>0.3262</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>0.0621</v>
+        <v>0.0654</v>
       </c>
       <c r="G32" s="2" t="n">
         <v>0.8484</v>
@@ -1492,7 +1492,7 @@
         <v>0.9648</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.9872</v>
+        <v>0.9957</v>
       </c>
     </row>
     <row r="33">
@@ -1506,13 +1506,13 @@
         <v>0.6539</v>
       </c>
       <c r="D33" s="2" t="n">
-        <v>0.3699</v>
+        <v>0.3733</v>
       </c>
       <c r="E33" s="2" t="n">
         <v>0.3848</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>0.1008</v>
+        <v>0.1042</v>
       </c>
       <c r="G33" s="2" t="n">
         <v>0.8433</v>
@@ -1524,7 +1524,7 @@
         <v>0.9666</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.9864000000000001</v>
+        <v>0.9954</v>
       </c>
     </row>
     <row r="34">
@@ -1535,16 +1535,16 @@
         <v>0.2436</v>
       </c>
       <c r="C34" s="2" t="n">
-        <v>0.6481</v>
+        <v>0.648</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>0.3458</v>
+        <v>0.3492</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>0.4045</v>
+        <v>0.4044</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>0.1022</v>
+        <v>0.1056</v>
       </c>
       <c r="G34" s="2" t="n">
         <v>0.8383</v>
@@ -1556,7 +1556,7 @@
         <v>0.9686</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.9855</v>
+        <v>0.9951</v>
       </c>
     </row>
     <row r="35">
@@ -1570,13 +1570,13 @@
         <v>0.6413</v>
       </c>
       <c r="D35" s="2" t="n">
-        <v>0.3219</v>
+        <v>0.3252</v>
       </c>
       <c r="E35" s="2" t="n">
         <v>0.4253</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>0.1059</v>
+        <v>0.1092</v>
       </c>
       <c r="G35" s="2" t="n">
         <v>0.8333</v>
@@ -1588,7 +1588,7 @@
         <v>0.9707</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.9846</v>
+        <v>0.9948</v>
       </c>
     </row>
     <row r="36">
@@ -1599,16 +1599,16 @@
         <v>0.2154</v>
       </c>
       <c r="C36" s="2" t="n">
-        <v>0.6365</v>
+        <v>0.6364</v>
       </c>
       <c r="D36" s="2" t="n">
-        <v>0.2983</v>
+        <v>0.3016</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>0.4211</v>
+        <v>0.421</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>0.0829</v>
+        <v>0.0862</v>
       </c>
       <c r="G36" s="2" t="n">
         <v>0.8282</v>
@@ -1620,7 +1620,7 @@
         <v>0.9731</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.9836</v>
+        <v>0.9945000000000001</v>
       </c>
     </row>
     <row r="37">
@@ -1634,13 +1634,13 @@
         <v>0.6327</v>
       </c>
       <c r="D37" s="2" t="n">
-        <v>0.275</v>
+        <v>0.2782</v>
       </c>
       <c r="E37" s="2" t="n">
         <v>0.4306</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>0.07290000000000001</v>
+        <v>0.0761</v>
       </c>
       <c r="G37" s="2" t="n">
         <v>0.8232</v>
@@ -1652,7 +1652,7 @@
         <v>0.9756</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.9827</v>
+        <v>0.9942</v>
       </c>
     </row>
     <row r="38">
@@ -1663,16 +1663,16 @@
         <v>0.1635</v>
       </c>
       <c r="C38" s="2" t="n">
-        <v>0.627</v>
+        <v>0.6269</v>
       </c>
       <c r="D38" s="2" t="n">
-        <v>0.252</v>
+        <v>0.2551</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>0.4635</v>
+        <v>0.4634</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>0.0885</v>
+        <v>0.0916</v>
       </c>
       <c r="G38" s="2" t="n">
         <v>0.8182</v>
@@ -1684,7 +1684,7 @@
         <v>0.9781</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.9817</v>
+        <v>0.9939</v>
       </c>
     </row>
     <row r="39">
@@ -1698,13 +1698,13 @@
         <v>0.6203</v>
       </c>
       <c r="D39" s="2" t="n">
-        <v>0.2293</v>
+        <v>0.2323</v>
       </c>
       <c r="E39" s="2" t="n">
         <v>0.4866</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>0.0956</v>
+        <v>0.09859999999999999</v>
       </c>
       <c r="G39" s="2" t="n">
         <v>0.8132</v>
@@ -1716,7 +1716,7 @@
         <v>0.9806</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.9807</v>
+        <v>0.9935</v>
       </c>
     </row>
     <row r="40">
@@ -1730,13 +1730,13 @@
         <v>0.6149</v>
       </c>
       <c r="D40" s="2" t="n">
-        <v>0.2071</v>
+        <v>0.21</v>
       </c>
       <c r="E40" s="2" t="n">
         <v>0.4989</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>0.0911</v>
+        <v>0.094</v>
       </c>
       <c r="G40" s="2" t="n">
         <v>0.8082</v>
@@ -1748,7 +1748,7 @@
         <v>0.9832</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.9796</v>
+        <v>0.9932</v>
       </c>
     </row>
     <row r="41">
@@ -1759,16 +1759,16 @@
         <v>0.1214</v>
       </c>
       <c r="C41" s="2" t="n">
-        <v>0.6101</v>
+        <v>0.61</v>
       </c>
       <c r="D41" s="2" t="n">
-        <v>0.1853</v>
+        <v>0.188</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>0.4887</v>
+        <v>0.4886</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>0.0639</v>
+        <v>0.06660000000000001</v>
       </c>
       <c r="G41" s="2" t="n">
         <v>0.8032</v>
@@ -1780,7 +1780,7 @@
         <v>0.9857</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.9785</v>
+        <v>0.9928</v>
       </c>
     </row>
     <row r="42">
@@ -1791,16 +1791,16 @@
         <v>0.107</v>
       </c>
       <c r="C42" s="2" t="n">
-        <v>0.6047</v>
+        <v>0.6046</v>
       </c>
       <c r="D42" s="2" t="n">
-        <v>0.164</v>
+        <v>0.1665</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>0.4977</v>
+        <v>0.4976</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>0.057</v>
+        <v>0.0595</v>
       </c>
       <c r="G42" s="2" t="n">
         <v>0.7982</v>
@@ -1812,7 +1812,7 @@
         <v>0.9881</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.9774</v>
+        <v>0.9923999999999999</v>
       </c>
     </row>
     <row r="43">
@@ -1823,16 +1823,16 @@
         <v>0.08939999999999999</v>
       </c>
       <c r="C43" s="2" t="n">
-        <v>0.5991</v>
+        <v>0.599</v>
       </c>
       <c r="D43" s="2" t="n">
-        <v>0.1432</v>
+        <v>0.1455</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>0.5097</v>
+        <v>0.5096000000000001</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>0.0538</v>
+        <v>0.0561</v>
       </c>
       <c r="G43" s="2" t="n">
         <v>0.7932</v>
@@ -1844,7 +1844,7 @@
         <v>0.9903999999999999</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.9762999999999999</v>
+        <v>0.992</v>
       </c>
     </row>
     <row r="44">
@@ -1858,13 +1858,13 @@
         <v>0.5939</v>
       </c>
       <c r="D44" s="2" t="n">
-        <v>0.1229</v>
+        <v>0.125</v>
       </c>
       <c r="E44" s="2" t="n">
         <v>0.5362</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>0.06519999999999999</v>
+        <v>0.0673</v>
       </c>
       <c r="G44" s="2" t="n">
         <v>0.7882</v>
@@ -1876,7 +1876,7 @@
         <v>0.9925</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.9751</v>
+        <v>0.9916</v>
       </c>
     </row>
     <row r="45">
@@ -1890,13 +1890,13 @@
         <v>0.5888</v>
       </c>
       <c r="D45" s="2" t="n">
-        <v>0.1032</v>
+        <v>0.1051</v>
       </c>
       <c r="E45" s="2" t="n">
         <v>0.5302</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>0.0446</v>
+        <v>0.0465</v>
       </c>
       <c r="G45" s="2" t="n">
         <v>0.7832</v>
@@ -1908,7 +1908,7 @@
         <v>0.9944</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.974</v>
+        <v>0.9912</v>
       </c>
     </row>
     <row r="46">
@@ -1922,13 +1922,13 @@
         <v>0.5839</v>
       </c>
       <c r="D46" s="2" t="n">
-        <v>0.0842</v>
+        <v>0.0858</v>
       </c>
       <c r="E46" s="2" t="n">
         <v>0.5386</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>0.0389</v>
+        <v>0.0405</v>
       </c>
       <c r="G46" s="2" t="n">
         <v>0.7782</v>
@@ -1940,7 +1940,7 @@
         <v>0.996</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.9727</v>
+        <v>0.9908</v>
       </c>
     </row>
     <row r="47">
@@ -1954,13 +1954,13 @@
         <v>0.579</v>
       </c>
       <c r="D47" s="2" t="n">
-        <v>0.0659</v>
+        <v>0.0672</v>
       </c>
       <c r="E47" s="2" t="n">
         <v>0.5427</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>0.0296</v>
+        <v>0.0309</v>
       </c>
       <c r="G47" s="2" t="n">
         <v>0.7732</v>
@@ -1972,7 +1972,7 @@
         <v>0.9974</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.9715</v>
+        <v>0.9903999999999999</v>
       </c>
     </row>
     <row r="48">
@@ -1983,16 +1983,16 @@
         <v>0.0365</v>
       </c>
       <c r="C48" s="2" t="n">
-        <v>0.5742</v>
+        <v>0.5741000000000001</v>
       </c>
       <c r="D48" s="2" t="n">
-        <v>0.0482</v>
+        <v>0.0492</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>0.5377</v>
+        <v>0.5376</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>0.0117</v>
+        <v>0.0127</v>
       </c>
       <c r="G48" s="2" t="n">
         <v>0.7682</v>
@@ -2004,7 +2004,7 @@
         <v>0.9985000000000001</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.9702</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="49">
@@ -2015,16 +2015,16 @@
         <v>0.0181</v>
       </c>
       <c r="C49" s="2" t="n">
-        <v>0.5694</v>
+        <v>0.5693</v>
       </c>
       <c r="D49" s="2" t="n">
-        <v>0.0314</v>
+        <v>0.032</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>0.5513</v>
+        <v>0.5512</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>0.0133</v>
+        <v>0.0139</v>
       </c>
       <c r="G49" s="2" t="n">
         <v>0.7632</v>
@@ -2036,7 +2036,7 @@
         <v>0.9993</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.969</v>
+        <v>0.9895</v>
       </c>
     </row>
     <row r="50">
@@ -2047,16 +2047,16 @@
         <v>0.0171</v>
       </c>
       <c r="C50" s="2" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.5639</v>
       </c>
       <c r="D50" s="2" t="n">
-        <v>0.0153</v>
+        <v>0.0156</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>0.5469000000000001</v>
+        <v>0.5468</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>-0.0018</v>
+        <v>-0.0015</v>
       </c>
       <c r="G50" s="2" t="n">
         <v>0.7583</v>
@@ -2068,7 +2068,7 @@
         <v>0.9998</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.9676</v>
+        <v>0.9891</v>
       </c>
     </row>
     <row r="51">
@@ -2079,13 +2079,13 @@
         <v>0.001</v>
       </c>
       <c r="C51" s="2" t="n">
-        <v>0.5585</v>
+        <v>0.5584</v>
       </c>
       <c r="D51" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>0.5575</v>
+        <v>0.5574</v>
       </c>
       <c r="F51" s="2" t="n">
         <v>-0.001</v>
@@ -2100,7 +2100,7 @@
         <v>1</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.9663</v>
+        <v>0.9886</v>
       </c>
     </row>
   </sheetData>
@@ -2248,7 +2248,7 @@
         <v>0.417</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.6835</v>
+        <v>0.6834</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>0.9915</v>
@@ -2268,7 +2268,7 @@
         <v>0.583</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.6778999999999999</v>
+        <v>0.6778</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>0.9833</v>

--- a/scenarios/07_karen_test_engineer/7.3_mtf_measurement_vs_prediction/outputs/mtf_comparison_results.xlsx
+++ b/scenarios/07_karen_test_engineer/7.3_mtf_measurement_vs_prediction/outputs/mtf_comparison_results.xlsx
@@ -543,13 +543,13 @@
         <v>0.9782999999999999</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>0.9066</v>
+        <v>0.9053</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>0.9941</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>-0.0717</v>
+        <v>-0.073</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>0.0158</v>
@@ -575,13 +575,13 @@
         <v>0.997</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>0.8164</v>
+        <v>0.8138</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>0.9865</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>-0.1806</v>
+        <v>-0.1832</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>-0.0105</v>
@@ -607,13 +607,13 @@
         <v>0.9897</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>0.8088</v>
+        <v>0.8026</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>0.9772999999999999</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>-0.1809</v>
+        <v>-0.1871</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>-0.0124</v>
@@ -639,13 +639,13 @@
         <v>0.9342</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>0.8013</v>
+        <v>0.7913</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>0.9665</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>-0.1329</v>
+        <v>-0.1429</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>0.0323</v>
@@ -671,13 +671,13 @@
         <v>0.93</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>0.795</v>
+        <v>0.779</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>0.9540999999999999</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>-0.135</v>
+        <v>-0.151</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>0.0241</v>
@@ -703,13 +703,13 @@
         <v>0.9357</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>0.789</v>
+        <v>0.7669</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>0.9404</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>-0.1467</v>
+        <v>-0.1688</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>0.0047</v>
@@ -735,13 +735,13 @@
         <v>0.9115</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>0.7853</v>
+        <v>0.7551</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>0.9252</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>-0.1262</v>
+        <v>-0.1564</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>0.0137</v>
@@ -767,13 +767,13 @@
         <v>0.8969</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>0.7814</v>
+        <v>0.7427</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>0.9088000000000001</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>-0.1155</v>
+        <v>-0.1542</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>0.0119</v>
@@ -799,13 +799,13 @@
         <v>0.8637</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>0.776</v>
+        <v>0.7272999999999999</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>0.8912</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>-0.0877</v>
+        <v>-0.1364</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>0.0275</v>
@@ -831,13 +831,13 @@
         <v>0.8677</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>0.7704</v>
+        <v>0.7114</v>
       </c>
       <c r="D12" s="2" t="n">
         <v>0.8725000000000001</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>-0.0973</v>
+        <v>-0.1563</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>0.0048</v>
@@ -863,13 +863,13 @@
         <v>0.8428</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>0.7637</v>
+        <v>0.6931</v>
       </c>
       <c r="D13" s="2" t="n">
         <v>0.8528</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>-0.0791</v>
+        <v>-0.1497</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>0.01</v>
@@ -895,13 +895,13 @@
         <v>0.8076</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>0.7576000000000001</v>
+        <v>0.6749000000000001</v>
       </c>
       <c r="D14" s="2" t="n">
         <v>0.8323</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>-0.05</v>
+        <v>-0.1327</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>0.0247</v>
@@ -927,13 +927,13 @@
         <v>0.7979000000000001</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>0.7531</v>
+        <v>0.6571</v>
       </c>
       <c r="D15" s="2" t="n">
         <v>0.8109</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>-0.0448</v>
+        <v>-0.1408</v>
       </c>
       <c r="F15" s="2" t="n">
         <v>0.013</v>
@@ -959,13 +959,13 @@
         <v>0.7615</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>0.7482</v>
+        <v>0.6385</v>
       </c>
       <c r="D16" s="2" t="n">
         <v>0.7887999999999999</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>-0.0133</v>
+        <v>-0.123</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>0.0273</v>
@@ -991,13 +991,13 @@
         <v>0.7141999999999999</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>0.7418</v>
+        <v>0.6177</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>0.766</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>0.0276</v>
+        <v>-0.0965</v>
       </c>
       <c r="F17" s="2" t="n">
         <v>0.0518</v>
@@ -1023,13 +1023,13 @@
         <v>0.7046</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>0.7356</v>
+        <v>0.5967</v>
       </c>
       <c r="D18" s="2" t="n">
         <v>0.7428</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>0.031</v>
+        <v>-0.1079</v>
       </c>
       <c r="F18" s="2" t="n">
         <v>0.0382</v>
@@ -1055,13 +1055,13 @@
         <v>0.656</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>0.7298</v>
+        <v>0.5753</v>
       </c>
       <c r="D19" s="2" t="n">
         <v>0.7191</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>0.0738</v>
+        <v>-0.08069999999999999</v>
       </c>
       <c r="F19" s="2" t="n">
         <v>0.0631</v>
@@ -1087,13 +1087,13 @@
         <v>0.6545</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>0.7238</v>
+        <v>0.5536</v>
       </c>
       <c r="D20" s="2" t="n">
         <v>0.695</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>0.0693</v>
+        <v>-0.1009</v>
       </c>
       <c r="F20" s="2" t="n">
         <v>0.0405</v>
@@ -1119,13 +1119,13 @@
         <v>0.6112</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>0.7176</v>
+        <v>0.5312</v>
       </c>
       <c r="D21" s="2" t="n">
         <v>0.6706</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>0.1064</v>
+        <v>-0.08</v>
       </c>
       <c r="F21" s="2" t="n">
         <v>0.0594</v>
@@ -1151,13 +1151,13 @@
         <v>0.5796</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>0.7124</v>
+        <v>0.5093</v>
       </c>
       <c r="D22" s="2" t="n">
         <v>0.646</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>0.1328</v>
+        <v>-0.0703</v>
       </c>
       <c r="F22" s="2" t="n">
         <v>0.0664</v>
@@ -1183,13 +1183,13 @@
         <v>0.5425</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>0.7089</v>
+        <v>0.4881</v>
       </c>
       <c r="D23" s="2" t="n">
         <v>0.6212</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>0.1664</v>
+        <v>-0.0544</v>
       </c>
       <c r="F23" s="2" t="n">
         <v>0.07870000000000001</v>
@@ -1215,13 +1215,13 @@
         <v>0.5414</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>0.7043</v>
+        <v>0.4661</v>
       </c>
       <c r="D24" s="2" t="n">
         <v>0.5963000000000001</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>0.1629</v>
+        <v>-0.07530000000000001</v>
       </c>
       <c r="F24" s="2" t="n">
         <v>0.0549</v>
@@ -1247,13 +1247,13 @@
         <v>0.4913</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>0.6983</v>
+        <v>0.4429</v>
       </c>
       <c r="D25" s="2" t="n">
         <v>0.5714</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>0.207</v>
+        <v>-0.0484</v>
       </c>
       <c r="F25" s="2" t="n">
         <v>0.0801</v>
@@ -1279,13 +1279,13 @@
         <v>0.458</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>0.6923</v>
+        <v>0.4196</v>
       </c>
       <c r="D26" s="2" t="n">
         <v>0.5464</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>0.2343</v>
+        <v>-0.0384</v>
       </c>
       <c r="F26" s="2" t="n">
         <v>0.08840000000000001</v>
@@ -1311,13 +1311,13 @@
         <v>0.4303</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>0.6863</v>
+        <v>0.3963</v>
       </c>
       <c r="D27" s="2" t="n">
         <v>0.5214</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>0.256</v>
+        <v>-0.034</v>
       </c>
       <c r="F27" s="2" t="n">
         <v>0.0911</v>
@@ -1343,13 +1343,13 @@
         <v>0.4152</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>0.6802</v>
+        <v>0.3731</v>
       </c>
       <c r="D28" s="2" t="n">
         <v>0.4964</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>0.265</v>
+        <v>-0.0421</v>
       </c>
       <c r="F28" s="2" t="n">
         <v>0.08119999999999999</v>
@@ -1375,13 +1375,13 @@
         <v>0.3849</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>0.6741</v>
+        <v>0.3499</v>
       </c>
       <c r="D29" s="2" t="n">
         <v>0.4716</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>0.2892</v>
+        <v>-0.035</v>
       </c>
       <c r="F29" s="2" t="n">
         <v>0.0867</v>
@@ -1407,13 +1407,13 @@
         <v>0.3584</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>0.6684</v>
+        <v>0.3271</v>
       </c>
       <c r="D30" s="2" t="n">
         <v>0.4468</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>0.31</v>
+        <v>-0.0313</v>
       </c>
       <c r="F30" s="2" t="n">
         <v>0.08840000000000001</v>
@@ -1439,13 +1439,13 @@
         <v>0.3322</v>
       </c>
       <c r="C31" s="2" t="n">
-        <v>0.6632</v>
+        <v>0.3048</v>
       </c>
       <c r="D31" s="2" t="n">
         <v>0.4221</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>0.331</v>
+        <v>-0.0274</v>
       </c>
       <c r="F31" s="2" t="n">
         <v>0.08989999999999999</v>
@@ -1471,13 +1471,13 @@
         <v>0.3322</v>
       </c>
       <c r="C32" s="2" t="n">
-        <v>0.6584</v>
+        <v>0.2829</v>
       </c>
       <c r="D32" s="2" t="n">
         <v>0.3976</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>0.3262</v>
+        <v>-0.0493</v>
       </c>
       <c r="F32" s="2" t="n">
         <v>0.0654</v>
@@ -1503,13 +1503,13 @@
         <v>0.2691</v>
       </c>
       <c r="C33" s="2" t="n">
-        <v>0.6539</v>
+        <v>0.2613</v>
       </c>
       <c r="D33" s="2" t="n">
         <v>0.3733</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>0.3848</v>
+        <v>-0.0078</v>
       </c>
       <c r="F33" s="2" t="n">
         <v>0.1042</v>
@@ -1535,13 +1535,13 @@
         <v>0.2436</v>
       </c>
       <c r="C34" s="2" t="n">
-        <v>0.648</v>
+        <v>0.2396</v>
       </c>
       <c r="D34" s="2" t="n">
         <v>0.3492</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>0.4044</v>
+        <v>-0.004</v>
       </c>
       <c r="F34" s="2" t="n">
         <v>0.1056</v>
@@ -1567,13 +1567,13 @@
         <v>0.216</v>
       </c>
       <c r="C35" s="2" t="n">
-        <v>0.6413</v>
+        <v>0.2179</v>
       </c>
       <c r="D35" s="2" t="n">
         <v>0.3252</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>0.4253</v>
+        <v>0.0019</v>
       </c>
       <c r="F35" s="2" t="n">
         <v>0.1092</v>
@@ -1599,13 +1599,13 @@
         <v>0.2154</v>
       </c>
       <c r="C36" s="2" t="n">
-        <v>0.6364</v>
+        <v>0.1974</v>
       </c>
       <c r="D36" s="2" t="n">
         <v>0.3016</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>0.421</v>
+        <v>-0.018</v>
       </c>
       <c r="F36" s="2" t="n">
         <v>0.0862</v>
@@ -1631,13 +1631,13 @@
         <v>0.2021</v>
       </c>
       <c r="C37" s="2" t="n">
-        <v>0.6327</v>
+        <v>0.1776</v>
       </c>
       <c r="D37" s="2" t="n">
         <v>0.2782</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>0.4306</v>
+        <v>-0.0245</v>
       </c>
       <c r="F37" s="2" t="n">
         <v>0.0761</v>
@@ -1663,13 +1663,13 @@
         <v>0.1635</v>
       </c>
       <c r="C38" s="2" t="n">
-        <v>0.6269</v>
+        <v>0.1579</v>
       </c>
       <c r="D38" s="2" t="n">
         <v>0.2551</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>0.4634</v>
+        <v>-0.0056</v>
       </c>
       <c r="F38" s="2" t="n">
         <v>0.0916</v>
@@ -1695,13 +1695,13 @@
         <v>0.1337</v>
       </c>
       <c r="C39" s="2" t="n">
-        <v>0.6203</v>
+        <v>0.1383</v>
       </c>
       <c r="D39" s="2" t="n">
         <v>0.2323</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>0.4866</v>
+        <v>0.0046</v>
       </c>
       <c r="F39" s="2" t="n">
         <v>0.09859999999999999</v>
@@ -1727,13 +1727,13 @@
         <v>0.116</v>
       </c>
       <c r="C40" s="2" t="n">
-        <v>0.6149</v>
+        <v>0.1199</v>
       </c>
       <c r="D40" s="2" t="n">
         <v>0.21</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>0.4989</v>
+        <v>0.0039</v>
       </c>
       <c r="F40" s="2" t="n">
         <v>0.094</v>
@@ -1759,13 +1759,13 @@
         <v>0.1214</v>
       </c>
       <c r="C41" s="2" t="n">
-        <v>0.61</v>
+        <v>0.1019</v>
       </c>
       <c r="D41" s="2" t="n">
         <v>0.188</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>0.4886</v>
+        <v>-0.0195</v>
       </c>
       <c r="F41" s="2" t="n">
         <v>0.06660000000000001</v>
@@ -1791,13 +1791,13 @@
         <v>0.107</v>
       </c>
       <c r="C42" s="2" t="n">
-        <v>0.6046</v>
+        <v>0.0848</v>
       </c>
       <c r="D42" s="2" t="n">
         <v>0.1665</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>0.4976</v>
+        <v>-0.0222</v>
       </c>
       <c r="F42" s="2" t="n">
         <v>0.0595</v>
@@ -1823,13 +1823,13 @@
         <v>0.08939999999999999</v>
       </c>
       <c r="C43" s="2" t="n">
-        <v>0.599</v>
+        <v>0.068</v>
       </c>
       <c r="D43" s="2" t="n">
         <v>0.1455</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>0.5096000000000001</v>
+        <v>-0.0214</v>
       </c>
       <c r="F43" s="2" t="n">
         <v>0.0561</v>
@@ -1855,13 +1855,13 @@
         <v>0.0577</v>
       </c>
       <c r="C44" s="2" t="n">
-        <v>0.5939</v>
+        <v>0.0523</v>
       </c>
       <c r="D44" s="2" t="n">
         <v>0.125</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>0.5362</v>
+        <v>-0.0054</v>
       </c>
       <c r="F44" s="2" t="n">
         <v>0.0673</v>
@@ -1887,13 +1887,13 @@
         <v>0.0586</v>
       </c>
       <c r="C45" s="2" t="n">
-        <v>0.5888</v>
+        <v>0.037</v>
       </c>
       <c r="D45" s="2" t="n">
         <v>0.1051</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>0.5302</v>
+        <v>-0.0216</v>
       </c>
       <c r="F45" s="2" t="n">
         <v>0.0465</v>
@@ -1919,13 +1919,13 @@
         <v>0.0453</v>
       </c>
       <c r="C46" s="2" t="n">
-        <v>0.5839</v>
+        <v>0.0228</v>
       </c>
       <c r="D46" s="2" t="n">
         <v>0.0858</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>0.5386</v>
+        <v>-0.0225</v>
       </c>
       <c r="F46" s="2" t="n">
         <v>0.0405</v>
@@ -1951,13 +1951,13 @@
         <v>0.0363</v>
       </c>
       <c r="C47" s="2" t="n">
-        <v>0.579</v>
+        <v>0.0089</v>
       </c>
       <c r="D47" s="2" t="n">
         <v>0.0672</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>0.5427</v>
+        <v>-0.0274</v>
       </c>
       <c r="F47" s="2" t="n">
         <v>0.0309</v>
@@ -1983,13 +1983,13 @@
         <v>0.0365</v>
       </c>
       <c r="C48" s="2" t="n">
-        <v>0.5741000000000001</v>
+        <v>0.0116</v>
       </c>
       <c r="D48" s="2" t="n">
         <v>0.0492</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>0.5376</v>
+        <v>-0.0249</v>
       </c>
       <c r="F48" s="2" t="n">
         <v>0.0127</v>
@@ -2015,13 +2015,13 @@
         <v>0.0181</v>
       </c>
       <c r="C49" s="2" t="n">
-        <v>0.5693</v>
+        <v>0.0169</v>
       </c>
       <c r="D49" s="2" t="n">
         <v>0.032</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>0.5512</v>
+        <v>-0.0012</v>
       </c>
       <c r="F49" s="2" t="n">
         <v>0.0139</v>
@@ -2047,13 +2047,13 @@
         <v>0.0171</v>
       </c>
       <c r="C50" s="2" t="n">
-        <v>0.5639</v>
+        <v>0.0272</v>
       </c>
       <c r="D50" s="2" t="n">
         <v>0.0156</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>0.5468</v>
+        <v>0.0101</v>
       </c>
       <c r="F50" s="2" t="n">
         <v>-0.0015</v>
@@ -2079,13 +2079,13 @@
         <v>0.001</v>
       </c>
       <c r="C51" s="2" t="n">
-        <v>0.5584</v>
+        <v>0.0381</v>
       </c>
       <c r="D51" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>0.5574</v>
+        <v>0.0371</v>
       </c>
       <c r="F51" s="2" t="n">
         <v>-0.001</v>
@@ -2168,7 +2168,7 @@
         <v>0</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.6893</v>
+        <v>0.408</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>1</v>
@@ -2188,7 +2188,7 @@
         <v>0.083</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.6891</v>
+        <v>0.4078</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>0.9997</v>
@@ -2208,7 +2208,7 @@
         <v>0.167</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.6884</v>
+        <v>0.4074</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>0.9986</v>
@@ -2228,7 +2228,7 @@
         <v>0.25</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.6872</v>
+        <v>0.4067</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>0.9969</v>
@@ -2248,7 +2248,7 @@
         <v>0.417</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.6834</v>
+        <v>0.4045</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>0.9915</v>
@@ -2268,7 +2268,7 @@
         <v>0.583</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.6778</v>
+        <v>0.4012</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>0.9833</v>
@@ -2288,7 +2288,7 @@
         <v>0.833</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0.6661</v>
+        <v>0.3942</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>0.9663</v>
@@ -2308,7 +2308,7 @@
         <v>1.25</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>0.6382</v>
+        <v>0.3777</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>0.9258</v>
@@ -2328,7 +2328,7 @@
         <v>1.667</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>0.601</v>
+        <v>0.3557</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>0.8719</v>
